--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1269,7 +1269,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$130</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5830" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5262" uniqueCount="777">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2439,69 +2439,6 @@
   </si>
   <si>
     <t>Observation.component:va-pre-condition-device.referenceRange</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size</t>
-  </si>
-  <si>
-    <t>va-cuff-size</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="8358-4"/&gt;
-    &lt;display value="Blood pressure device cuff size"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>1805-1: fixed value = http://loinc.org#8358-4 Blood pressure device cuff size</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
-  </si>
-  <si>
-    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2818,7 +2755,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR144"/>
+  <dimension ref="A1:AR130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -19296,1788 +19233,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="D131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="P131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AP131" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="AQ131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR131" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AQ132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR132" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AQ133" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR133" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="P134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP134" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AQ134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR134" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="P135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AP135" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AQ135" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AR135" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="P136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AC136" s="2"/>
-      <c r="AD136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AP136" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AQ136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR136" t="s" s="2">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="D137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="P137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AP137" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AQ137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR137" t="s" s="2">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP138" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AQ138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR138" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP139" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AQ139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR139" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="P140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y140" s="2"/>
-      <c r="Z140" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AP140" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AQ140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR140" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="P141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AP141" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AQ141" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR141" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="P142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AP142" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AQ142" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR142" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="143" hidden="true">
-      <c r="A143" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="P143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AP143" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AQ143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR143" t="s" s="2">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="144" hidden="true">
-      <c r="A144" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="P144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AP144" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AQ144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR144" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AR144">
+  <autoFilter ref="A1:AR130">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21087,7 +19244,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI143">
+  <conditionalFormatting sqref="A2:AI129">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -561,7 +561,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsMeasurementDevice</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsMeasurementDevice</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -605,7 +605,7 @@
     <t>Observation.extension:observation-bodyPosition.value[x]</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsBodyPosition</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsBodyPosition</t>
   </si>
   <si>
     <t>1804: terminologyMaps using VF_VitalsBodyPosition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -1254,7 +1254,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsCodes</t>
   </si>
   <si>
     <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
@@ -1762,7 +1762,7 @@
 </t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFVitalsUnits</t>
+    <t>http://va.gov/fhir/ConceptMap/VitalsUnits</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.code.value</t>
@@ -1884,7 +1884,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsBodySite</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsBodySite</t>
   </si>
   <si>
     <t>662: terminologyMaps using VF_VitalsBodySite on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -1917,7 +1917,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsMethod</t>
   </si>
   <si>
     <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -2366,7 +2366,7 @@
     <t>Observation.component.value[x].coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPrecondition</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsPrecondition</t>
   </si>
   <si>
     <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -2423,7 +2423,7 @@
     <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsQualifyingDevice</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsQualifyingDevice</t>
   </si>
   <si>
     <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -2783,7 +2783,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5262" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5262" uniqueCount="778">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -916,6 +916,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSigns-655:if null then fixed value #final {null}VitalSigns-656:if not null then fixed value #entered-in-error {null}</t>
   </si>
   <si>
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
@@ -2336,7 +2340,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>1802-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+    <t>1802-1: fixed value = http://loinc.org#104158-1 "Associated precondition - Reported"</t>
   </si>
   <si>
     <t>Observation.component:va-pre-condition.value[x]</t>
@@ -2405,7 +2409,7 @@
     <t>Observation.component:va-pre-condition-device.code</t>
   </si>
   <si>
-    <t>1803-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+    <t>1803-1: fixed value = http://loinc.org#104158-1 "Associated precondition - Reported"</t>
   </si>
   <si>
     <t>Observation.component:va-pre-condition-device.value[x]</t>
@@ -6798,28 +6802,28 @@
         <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>290</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6827,10 +6831,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6856,16 +6860,16 @@
         <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6875,7 +6879,7 @@
         <v>84</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>84</v>
@@ -6893,16 +6897,16 @@
         <v>118</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6912,7 +6916,7 @@
         <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6927,7 +6931,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6942,10 +6946,10 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6953,13 +6957,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -6984,16 +6988,16 @@
         <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -7021,10 +7025,10 @@
         <v>118</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -7042,7 +7046,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7072,10 +7076,10 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -7083,10 +7087,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7207,10 +7211,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7333,10 +7337,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7359,19 +7363,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7420,7 +7424,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7447,10 +7451,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7461,10 +7465,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7585,10 +7589,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7711,10 +7715,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7740,23 +7744,23 @@
         <v>108</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>84</v>
@@ -7798,7 +7802,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7825,10 +7829,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7839,10 +7843,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7868,13 +7872,13 @@
         <v>208</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7924,7 +7928,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7951,10 +7955,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7965,10 +7969,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7994,21 +7998,21 @@
         <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>84</v>
@@ -8050,7 +8054,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8077,10 +8081,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -8091,10 +8095,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8120,14 +8124,14 @@
         <v>208</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -8176,7 +8180,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8203,10 +8207,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8217,10 +8221,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8243,19 +8247,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8304,7 +8308,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8331,10 +8335,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8345,10 +8349,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8374,16 +8378,16 @@
         <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8432,7 +8436,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8459,10 +8463,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8473,14 +8477,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8502,16 +8506,16 @@
         <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8539,10 +8543,10 @@
         <v>226</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8560,7 +8564,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -8581,30 +8585,30 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8725,10 +8729,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8851,10 +8855,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8877,19 +8881,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8918,7 +8922,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8936,7 +8940,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8951,10 +8955,10 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>84</v>
@@ -8963,10 +8967,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8977,10 +8981,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9006,16 +9010,16 @@
         <v>208</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9064,7 +9068,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9091,10 +9095,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -9105,10 +9109,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9131,19 +9135,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9192,7 +9196,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9207,25 +9211,25 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9233,10 +9237,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9259,16 +9263,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9318,7 +9322,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9345,13 +9349,13 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9359,14 +9363,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9385,19 +9389,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9446,7 +9450,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9467,19 +9471,19 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>84</v>
@@ -9487,14 +9491,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9513,19 +9517,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9562,7 +9566,7 @@
         <v>84</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
@@ -9572,7 +9576,7 @@
         <v>143</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9581,10 +9585,10 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -9593,19 +9597,19 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -9613,16 +9617,16 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9641,19 +9645,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9702,7 +9706,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9711,31 +9715,31 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>84</v>
@@ -9743,10 +9747,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9769,16 +9773,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9828,7 +9832,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9843,10 +9847,10 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>84</v>
@@ -9855,13 +9859,13 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -9869,10 +9873,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9895,17 +9899,17 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9954,7 +9958,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9969,25 +9973,25 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>84</v>
@@ -9995,10 +9999,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10021,19 +10025,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -10061,16 +10065,16 @@
         <v>226</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
@@ -10080,7 +10084,7 @@
         <v>143</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10089,7 +10093,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -10104,30 +10108,30 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>84</v>
@@ -10149,19 +10153,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10189,10 +10193,10 @@
         <v>226</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -10210,7 +10214,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10219,7 +10223,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -10234,27 +10238,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10375,10 +10379,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10501,10 +10505,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10527,19 +10531,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10588,7 +10592,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10603,10 +10607,10 @@
         <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>84</v>
@@ -10615,10 +10619,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10629,10 +10633,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10658,20 +10662,20 @@
         <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>84</v>
@@ -10695,10 +10699,10 @@
         <v>174</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10716,7 +10720,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10743,10 +10747,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10757,10 +10761,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10786,14 +10790,14 @@
         <v>208</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10842,7 +10846,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10869,10 +10873,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10883,10 +10887,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10912,14 +10916,14 @@
         <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10968,7 +10972,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10977,7 +10981,7 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
@@ -10995,10 +10999,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -11009,10 +11013,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11038,16 +11042,16 @@
         <v>114</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11096,7 +11100,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11111,10 +11115,10 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>84</v>
@@ -11123,10 +11127,10 @@
         <v>84</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11137,10 +11141,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11166,10 +11170,10 @@
         <v>208</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11261,10 +11265,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11383,13 +11387,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>545</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>84</v>
@@ -11411,16 +11415,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11511,10 +11515,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11635,10 +11639,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11759,10 +11763,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11802,7 +11806,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>84</v>
@@ -11885,10 +11889,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11911,7 +11915,7 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>172</v>
@@ -11929,7 +11933,7 @@
         <v>84</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>84</v>
@@ -12009,10 +12013,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12038,10 +12042,10 @@
         <v>208</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12092,7 +12096,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12133,10 +12137,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12162,16 +12166,16 @@
         <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12199,10 +12203,10 @@
         <v>226</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -12220,7 +12224,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12229,13 +12233,13 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>84</v>
@@ -12250,7 +12254,7 @@
         <v>137</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12261,14 +12265,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12290,16 +12294,16 @@
         <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12327,10 +12331,10 @@
         <v>226</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12348,7 +12352,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12372,27 +12376,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12415,19 +12419,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12476,7 +12480,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12503,10 +12507,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12517,10 +12521,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12546,13 +12550,13 @@
         <v>171</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12582,7 +12586,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12600,7 +12604,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12615,7 +12619,7 @@
         <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>84</v>
@@ -12624,27 +12628,27 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12670,16 +12674,16 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12708,7 +12712,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12726,7 +12730,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12741,7 +12745,7 @@
         <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>84</v>
@@ -12753,10 +12757,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12767,10 +12771,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12793,16 +12797,16 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12852,7 +12856,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12876,27 +12880,27 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12919,16 +12923,16 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12978,7 +12982,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13002,27 +13006,27 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13045,19 +13049,19 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13106,7 +13110,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13118,7 +13122,7 @@
         <v>84</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>84</v>
@@ -13133,10 +13137,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13147,10 +13151,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13271,10 +13275,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13397,14 +13401,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13426,10 +13430,10 @@
         <v>139</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>195</v>
@@ -13484,7 +13488,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13525,10 +13529,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13551,13 +13555,13 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13608,7 +13612,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13617,7 +13621,7 @@
         <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>106</v>
@@ -13635,10 +13639,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13649,10 +13653,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13675,13 +13679,13 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13732,7 +13736,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13741,7 +13745,7 @@
         <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>106</v>
@@ -13759,10 +13763,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13773,10 +13777,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13802,16 +13806,16 @@
         <v>171</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13839,10 +13843,10 @@
         <v>118</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -13860,7 +13864,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13884,13 +13888,13 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13901,10 +13905,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13930,16 +13934,16 @@
         <v>171</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13964,13 +13968,13 @@
         <v>84</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>84</v>
@@ -13988,7 +13992,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14012,13 +14016,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14029,10 +14033,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14055,17 +14059,17 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14114,7 +14118,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14144,7 +14148,7 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14155,10 +14159,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14184,10 +14188,10 @@
         <v>208</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14238,7 +14242,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14265,10 +14269,10 @@
         <v>84</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14279,10 +14283,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14305,16 +14309,16 @@
         <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14364,7 +14368,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14391,10 +14395,10 @@
         <v>84</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14405,10 +14409,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14431,16 +14435,16 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14490,7 +14494,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14517,10 +14521,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14531,10 +14535,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14557,19 +14561,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14606,7 +14610,7 @@
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14616,7 +14620,7 @@
         <v>143</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14628,7 +14632,7 @@
         <v>84</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>84</v>
@@ -14643,10 +14647,10 @@
         <v>84</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14657,10 +14661,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14781,10 +14785,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14907,14 +14911,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14936,10 +14940,10 @@
         <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>195</v>
@@ -14994,7 +14998,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15035,10 +15039,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15064,16 +15068,16 @@
         <v>171</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15101,10 +15105,10 @@
         <v>226</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15122,7 +15126,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>94</v>
@@ -15146,16 +15150,16 @@
         <v>84</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>84</v>
@@ -15163,10 +15167,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15189,19 +15193,19 @@
         <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15229,10 +15233,10 @@
         <v>226</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>84</v>
@@ -15250,7 +15254,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15259,7 +15263,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -15274,27 +15278,27 @@
         <v>84</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15320,16 +15324,16 @@
         <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15357,10 +15361,10 @@
         <v>226</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15378,7 +15382,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15387,13 +15391,13 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15408,7 +15412,7 @@
         <v>137</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15419,14 +15423,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15448,16 +15452,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15485,10 +15489,10 @@
         <v>226</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15506,7 +15510,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15530,27 +15534,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15576,16 +15580,16 @@
         <v>85</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15634,7 +15638,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15661,10 +15665,10 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15675,13 +15679,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>84</v>
@@ -15703,19 +15707,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15764,7 +15768,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15776,7 +15780,7 @@
         <v>84</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>84</v>
@@ -15791,10 +15795,10 @@
         <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15805,10 +15809,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15929,10 +15933,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16055,14 +16059,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -16084,10 +16088,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>195</v>
@@ -16142,7 +16146,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16183,10 +16187,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16212,16 +16216,16 @@
         <v>171</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16231,7 +16235,7 @@
         <v>84</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>84</v>
@@ -16249,10 +16253,10 @@
         <v>226</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>84</v>
@@ -16270,7 +16274,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>94</v>
@@ -16285,7 +16289,7 @@
         <v>106</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>84</v>
@@ -16294,16 +16298,16 @@
         <v>84</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>84</v>
@@ -16311,10 +16315,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16337,19 +16341,19 @@
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -16377,16 +16381,16 @@
         <v>226</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
@@ -16396,7 +16400,7 @@
         <v>143</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16405,7 +16409,7 @@
         <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16420,30 +16424,30 @@
         <v>84</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>84</v>
@@ -16468,16 +16472,16 @@
         <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16505,10 +16509,10 @@
         <v>226</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>84</v>
@@ -16526,7 +16530,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16535,7 +16539,7 @@
         <v>94</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>106</v>
@@ -16550,27 +16554,27 @@
         <v>84</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16691,10 +16695,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16817,10 +16821,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16843,19 +16847,19 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -16884,7 +16888,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -16902,7 +16906,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -16917,7 +16921,7 @@
         <v>106</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>84</v>
@@ -16929,10 +16933,10 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -16943,10 +16947,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16972,16 +16976,16 @@
         <v>208</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -17030,7 +17034,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17057,10 +17061,10 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17071,10 +17075,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17100,16 +17104,16 @@
         <v>171</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
@@ -17137,10 +17141,10 @@
         <v>226</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>84</v>
@@ -17158,7 +17162,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17167,7 +17171,7 @@
         <v>94</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>106</v>
@@ -17188,7 +17192,7 @@
         <v>137</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17199,14 +17203,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17228,16 +17232,16 @@
         <v>171</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17265,10 +17269,10 @@
         <v>226</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>84</v>
@@ -17286,7 +17290,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17310,27 +17314,27 @@
         <v>84</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR115" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17356,16 +17360,16 @@
         <v>85</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17414,7 +17418,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17441,10 +17445,10 @@
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17455,13 +17459,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>84</v>
@@ -17483,19 +17487,19 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17544,7 +17548,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17556,7 +17560,7 @@
         <v>84</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>84</v>
@@ -17571,10 +17575,10 @@
         <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -17585,10 +17589,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17709,10 +17713,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17835,14 +17839,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17864,10 +17868,10 @@
         <v>139</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>195</v>
@@ -17922,7 +17926,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -17963,10 +17967,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17992,16 +17996,16 @@
         <v>171</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18011,7 +18015,7 @@
         <v>84</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>84</v>
@@ -18029,10 +18033,10 @@
         <v>226</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18050,7 +18054,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>94</v>
@@ -18065,7 +18069,7 @@
         <v>106</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>84</v>
@@ -18074,16 +18078,16 @@
         <v>84</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>84</v>
@@ -18091,10 +18095,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18117,19 +18121,19 @@
         <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18157,16 +18161,16 @@
         <v>226</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -18176,7 +18180,7 @@
         <v>143</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18185,7 +18189,7 @@
         <v>94</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>106</v>
@@ -18200,30 +18204,30 @@
         <v>84</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>84</v>
@@ -18248,16 +18252,16 @@
         <v>171</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18285,10 +18289,10 @@
         <v>226</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>84</v>
@@ -18306,7 +18310,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18315,7 +18319,7 @@
         <v>94</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>106</v>
@@ -18330,27 +18334,27 @@
         <v>84</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR123" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18471,10 +18475,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18597,10 +18601,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18623,19 +18627,19 @@
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18664,7 +18668,7 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18682,7 +18686,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18697,7 +18701,7 @@
         <v>106</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>84</v>
@@ -18709,10 +18713,10 @@
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
@@ -18723,10 +18727,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18752,16 +18756,16 @@
         <v>208</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
@@ -18810,7 +18814,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18837,10 +18841,10 @@
         <v>84</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
@@ -18851,10 +18855,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18880,16 +18884,16 @@
         <v>171</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -18917,10 +18921,10 @@
         <v>226</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>84</v>
@@ -18938,7 +18942,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -18947,7 +18951,7 @@
         <v>94</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>106</v>
@@ -18968,7 +18972,7 @@
         <v>137</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
@@ -18979,14 +18983,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -19008,16 +19012,16 @@
         <v>171</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19045,10 +19049,10 @@
         <v>226</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>84</v>
@@ -19066,7 +19070,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19090,27 +19094,27 @@
         <v>84</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19136,16 +19140,16 @@
         <v>85</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19194,7 +19198,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19221,10 +19225,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -919,7 +919,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSigns-655:if null then fixed value #final {null}VitalSigns-656:if not null then fixed value #entered-in-error {null}</t>
+vs-10-655:120.5-4: if null then #final {null}vs-10-656:120.5-4: if not null then #entered-in-error {null}</t>
   </si>
   <si>
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -577,6 +577,9 @@
     <t>663: terminologyMaps using VF_VitalsMeasurementDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
+    <t>Observation.ObservationMethods</t>
+  </si>
+  <si>
     <t>Observation.extension:observation-bodyPosition</t>
   </si>
   <si>
@@ -928,7 +931,7 @@
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
-    <t>vital.removed [m]</t>
+    <t>Observation.ObservationExtension.Removed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1273,7 +1276,7 @@
     <t>Vital.VitalSign.VitalTypeIEN</t>
   </si>
   <si>
-    <t>vital.vuid,vital.name,vital.high,vital.low,vital.bmi</t>
+    <t>Observation.ObservationCode,Observation.ObservationExtension.BMI</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1433,7 +1436,7 @@
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
   </si>
   <si>
-    <t>vital.taken</t>
+    <t>Observation.Observation.Description,Observation.ObservationMethod.Description</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1458,9 +1461,6 @@
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
   </si>
   <si>
-    <t>vital.entered</t>
-  </si>
-  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1492,7 +1492,7 @@
     <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
-    <t>vital.facility,vital.location</t>
+    <t>Observation.EnteredAt,Observation.ObservationExtension.Location</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1601,7 +1601,7 @@
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
-    <t>vital.value,vital.units,vital.metricvalue,vital.metricUnits,vital.bmi</t>
+    <t>Observation.ObservationValue,Observation.ObservationExtension.BMI</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -2820,7 +2820,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="150.6015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="60.49609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="76.37109375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -4608,7 +4608,7 @@
         <v>85</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>85</v>
@@ -4631,13 +4631,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>139</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>85</v>
@@ -4659,13 +4659,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4760,7 +4760,7 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>153</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>160</v>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>164</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>85</v>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>171</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>85</v>
@@ -5239,13 +5239,13 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>85</v>
@@ -5268,14 +5268,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -5297,16 +5297,16 @@
         <v>140</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>85</v>
@@ -5355,7 +5355,7 @@
         <v>85</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -5399,10 +5399,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5425,17 +5425,17 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>85</v>
@@ -5484,7 +5484,7 @@
         <v>85</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -5508,19 +5508,19 @@
         <v>85</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>85</v>
@@ -5528,10 +5528,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5554,7 +5554,7 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>154</v>
@@ -5655,14 +5655,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5684,13 +5684,13 @@
         <v>140</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5784,10 +5784,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5813,16 +5813,16 @@
         <v>115</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5850,10 +5850,10 @@
         <v>175</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5871,7 +5871,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5904,7 +5904,7 @@
         <v>138</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>85</v>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5944,16 +5944,16 @@
         <v>172</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5978,13 +5978,13 @@
         <v>85</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -6002,7 +6002,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -6032,10 +6032,10 @@
         <v>85</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>85</v>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6075,16 +6075,16 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>85</v>
@@ -6094,10 +6094,10 @@
         <v>85</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>85</v>
@@ -6133,7 +6133,7 @@
         <v>85</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -6148,7 +6148,7 @@
         <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>85</v>
@@ -6163,10 +6163,10 @@
         <v>85</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>85</v>
@@ -6177,10 +6177,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6203,16 +6203,16 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -6226,7 +6226,7 @@
         <v>85</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>85</v>
@@ -6262,7 +6262,7 @@
         <v>85</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -6277,7 +6277,7 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>85</v>
@@ -6292,10 +6292,10 @@
         <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>85</v>
@@ -6306,10 +6306,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6332,13 +6332,13 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6389,7 +6389,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -6419,10 +6419,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6459,16 +6459,16 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6518,7 +6518,7 @@
         <v>85</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -6548,10 +6548,10 @@
         <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>85</v>
@@ -6562,14 +6562,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -6588,17 +6588,17 @@
         <v>96</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>85</v>
@@ -6647,7 +6647,7 @@
         <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -6671,16 +6671,16 @@
         <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>85</v>
@@ -6691,14 +6691,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6717,16 +6717,16 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6776,7 +6776,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6800,16 +6800,16 @@
         <v>85</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6820,10 +6820,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6849,16 +6849,16 @@
         <v>115</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>85</v>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>85</v>
@@ -6905,7 +6905,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>95</v>
@@ -6917,31 +6917,31 @@
         <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>85</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6978,16 +6978,16 @@
         <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6997,7 +6997,7 @@
         <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>85</v>
@@ -7015,16 +7015,16 @@
         <v>119</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -7034,7 +7034,7 @@
         <v>144</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -7049,7 +7049,7 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -7067,10 +7067,10 @@
         <v>85</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AS33" t="s" s="2">
         <v>85</v>
@@ -7078,13 +7078,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>85</v>
@@ -7109,16 +7109,16 @@
         <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -7146,10 +7146,10 @@
         <v>119</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>85</v>
@@ -7167,7 +7167,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -7200,10 +7200,10 @@
         <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AS34" t="s" s="2">
         <v>85</v>
@@ -7211,10 +7211,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7237,7 +7237,7 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>154</v>
@@ -7338,14 +7338,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -7367,13 +7367,13 @@
         <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7467,10 +7467,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7493,19 +7493,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7554,7 +7554,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7584,10 +7584,10 @@
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7624,7 +7624,7 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>154</v>
@@ -7725,14 +7725,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7754,13 +7754,13 @@
         <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7854,10 +7854,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7883,23 +7883,23 @@
         <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>85</v>
@@ -7941,7 +7941,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7971,10 +7971,10 @@
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
@@ -7985,10 +7985,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8011,16 +8011,16 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8070,7 +8070,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -8100,10 +8100,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8143,21 +8143,21 @@
         <v>115</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>85</v>
@@ -8199,7 +8199,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -8229,10 +8229,10 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>85</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8269,17 +8269,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -8328,7 +8328,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -8358,10 +8358,10 @@
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>85</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8398,19 +8398,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8459,7 +8459,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8489,10 +8489,10 @@
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -8503,10 +8503,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8529,19 +8529,19 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8590,7 +8590,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8620,10 +8620,10 @@
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -8634,14 +8634,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8663,16 +8663,16 @@
         <v>172</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8697,13 +8697,13 @@
         <v>85</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -8721,7 +8721,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -8745,30 +8745,30 @@
         <v>85</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8791,7 +8791,7 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>154</v>
@@ -8892,14 +8892,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8921,13 +8921,13 @@
         <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9021,10 +9021,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9047,19 +9047,19 @@
         <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -9106,7 +9106,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9121,13 +9121,13 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>85</v>
@@ -9136,10 +9136,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9176,19 +9176,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -9237,7 +9237,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9267,10 +9267,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -9281,10 +9281,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9307,19 +9307,19 @@
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -9368,7 +9368,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9383,28 +9383,28 @@
         <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>85</v>
@@ -9412,10 +9412,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9438,16 +9438,16 @@
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9497,7 +9497,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9527,13 +9527,13 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>85</v>
@@ -9541,14 +9541,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9567,19 +9567,19 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9628,7 +9628,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9652,19 +9652,19 @@
         <v>85</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AS53" t="s" s="2">
         <v>85</v>
@@ -9672,14 +9672,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9698,19 +9698,19 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9747,7 +9747,7 @@
         <v>85</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
@@ -9757,7 +9757,7 @@
         <v>144</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9766,10 +9766,10 @@
         <v>95</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9781,19 +9781,19 @@
         <v>85</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AS54" t="s" s="2">
         <v>85</v>
@@ -9801,16 +9801,16 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9829,19 +9829,19 @@
         <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9890,7 +9890,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9899,34 +9899,34 @@
         <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>85</v>
@@ -9934,10 +9934,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9960,16 +9960,16 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10019,7 +10019,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -10034,13 +10034,13 @@
         <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>463</v>
+        <v>85</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>85</v>
@@ -10255,7 +10255,7 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>485</v>
@@ -10267,7 +10267,7 @@
         <v>85</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
@@ -10386,7 +10386,7 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>485</v>
@@ -10480,7 +10480,7 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>154</v>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10610,13 +10610,13 @@
         <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10998,7 +10998,7 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>525</v>
@@ -11335,10 +11335,10 @@
         <v>546</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>85</v>
@@ -11387,7 +11387,7 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>550</v>
@@ -12280,7 +12280,7 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>573</v>
@@ -12444,7 +12444,7 @@
         <v>85</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y75" t="s" s="2">
         <v>580</v>
@@ -12575,7 +12575,7 @@
         <v>85</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y76" t="s" s="2">
         <v>591</v>
@@ -12878,7 +12878,7 @@
         <v>85</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>85</v>
@@ -13007,7 +13007,7 @@
         <v>85</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>85</v>
@@ -13445,7 +13445,7 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>154</v>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -13575,13 +13575,13 @@
         <v>140</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13710,10 +13710,10 @@
         <v>656</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
@@ -14477,7 +14477,7 @@
         <v>85</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>693</v>
@@ -14991,7 +14991,7 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>154</v>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -15121,13 +15121,13 @@
         <v>140</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -15256,10 +15256,10 @@
         <v>656</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>85</v>
@@ -15415,13 +15415,13 @@
         <v>85</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>85</v>
@@ -15469,13 +15469,13 @@
         <v>726</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>85</v>
@@ -15546,7 +15546,7 @@
         <v>85</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y99" t="s" s="2">
         <v>485</v>
@@ -15677,7 +15677,7 @@
         <v>85</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y100" t="s" s="2">
         <v>580</v>
@@ -15808,7 +15808,7 @@
         <v>85</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y101" t="s" s="2">
         <v>591</v>
@@ -16166,7 +16166,7 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>154</v>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -16296,13 +16296,13 @@
         <v>140</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -16431,10 +16431,10 @@
         <v>656</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>85</v>
@@ -16590,13 +16590,13 @@
         <v>85</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>85</v>
@@ -16644,13 +16644,13 @@
         <v>726</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS107" t="s" s="2">
         <v>85</v>
@@ -16721,7 +16721,7 @@
         <v>85</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y108" t="s" s="2">
         <v>485</v>
@@ -16733,7 +16733,7 @@
         <v>85</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
@@ -16852,7 +16852,7 @@
         <v>85</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y109" t="s" s="2">
         <v>485</v>
@@ -16946,7 +16946,7 @@
         <v>85</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>154</v>
@@ -17054,7 +17054,7 @@
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -17076,13 +17076,13 @@
         <v>140</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -17202,19 +17202,19 @@
         <v>96</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>85</v>
@@ -17261,7 +17261,7 @@
         <v>85</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -17282,7 +17282,7 @@
         <v>85</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>85</v>
@@ -17291,10 +17291,10 @@
         <v>85</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>85</v>
@@ -17331,19 +17331,19 @@
         <v>96</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>85</v>
@@ -17392,7 +17392,7 @@
         <v>85</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
@@ -17422,10 +17422,10 @@
         <v>85</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>85</v>
@@ -17499,7 +17499,7 @@
         <v>85</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y114" t="s" s="2">
         <v>580</v>
@@ -17630,7 +17630,7 @@
         <v>85</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y115" t="s" s="2">
         <v>591</v>
@@ -17988,7 +17988,7 @@
         <v>85</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>154</v>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -18118,13 +18118,13 @@
         <v>140</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -18253,10 +18253,10 @@
         <v>656</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>85</v>
@@ -18412,13 +18412,13 @@
         <v>85</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>85</v>
@@ -18466,13 +18466,13 @@
         <v>726</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS121" t="s" s="2">
         <v>85</v>
@@ -18543,7 +18543,7 @@
         <v>85</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y122" t="s" s="2">
         <v>485</v>
@@ -18555,7 +18555,7 @@
         <v>85</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -18674,7 +18674,7 @@
         <v>85</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y123" t="s" s="2">
         <v>485</v>
@@ -18768,7 +18768,7 @@
         <v>85</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L124" t="s" s="2">
         <v>154</v>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -18898,13 +18898,13 @@
         <v>140</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -19024,19 +19024,19 @@
         <v>96</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>85</v>
@@ -19083,7 +19083,7 @@
         <v>85</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -19104,7 +19104,7 @@
         <v>85</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>85</v>
@@ -19113,10 +19113,10 @@
         <v>85</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>85</v>
@@ -19153,19 +19153,19 @@
         <v>96</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>85</v>
@@ -19214,7 +19214,7 @@
         <v>85</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -19244,10 +19244,10 @@
         <v>85</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>85</v>
@@ -19321,7 +19321,7 @@
         <v>85</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y128" t="s" s="2">
         <v>580</v>
@@ -19452,7 +19452,7 @@
         <v>85</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y129" t="s" s="2">
         <v>591</v>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -931,7 +931,7 @@
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
-    <t>Observation.ObservationExtension.Removed</t>
+    <t>Observation.Extension[ObservationExtension].Removed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1276,7 +1276,7 @@
     <t>Vital.VitalSign.VitalTypeIEN</t>
   </si>
   <si>
-    <t>Observation.ObservationCode,Observation.ObservationExtension.BMI</t>
+    <t>Observation.ObservationCode,Observation.Extension[ObservationExtension].BMI</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1436,7 +1436,7 @@
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
   </si>
   <si>
-    <t>Observation.Observation.Description,Observation.ObservationMethod.Description</t>
+    <t>Observation.ObservationCode[Observation].Description,Observation.ObservationMethods[ObservationMethod].Description</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1492,7 +1492,7 @@
     <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
-    <t>Observation.EnteredAt,Observation.ObservationExtension.Location</t>
+    <t>Observation.EnteredAt,Observation.Extension[ObservationExtension].Location</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1601,7 +1601,7 @@
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
-    <t>Observation.ObservationValue,Observation.ObservationExtension.BMI</t>
+    <t>Observation.ObservationValue,Observation.Extension[ObservationExtension].BMI</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -2820,7 +2820,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="150.6015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="76.37109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="114.0859375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-vital-signs</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-vital-signs.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$131</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5392" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5434" uniqueCount="787">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1787,7 +1787,7 @@
 </t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/VitalsUnits</t>
+    <t>http://va.gov/fhir/ConceptMap/VF-VitalsUnits</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.code.value</t>
@@ -2300,6 +2300,12 @@
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>2193: target not supported</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -2780,7 +2786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS130"/>
+  <dimension ref="A1:AS131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -15558,16 +15564,14 @@
         <v>85</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>727</v>
@@ -15617,9 +15621,11 @@
         <v>733</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>727</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>85</v>
       </c>
@@ -15637,22 +15643,22 @@
         <v>85</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>172</v>
+        <v>494</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>579</v>
+        <v>484</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>85</v>
@@ -15680,10 +15686,10 @@
         <v>228</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>580</v>
+        <v>485</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>581</v>
+        <v>486</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>85</v>
@@ -15701,7 +15707,7 @@
         <v>85</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15710,13 +15716,13 @@
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>85</v>
@@ -15728,41 +15734,41 @@
         <v>85</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>85</v>
+        <v>732</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>138</v>
+        <v>489</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>584</v>
+        <v>490</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS100" t="s" s="2">
-        <v>85</v>
+        <v>491</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>586</v>
+        <v>85</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>85</v>
@@ -15774,16 +15780,16 @@
         <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>587</v>
+        <v>736</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>588</v>
+        <v>737</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>589</v>
+        <v>738</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>85</v>
@@ -15811,10 +15817,10 @@
         <v>228</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>85</v>
@@ -15832,22 +15838,22 @@
         <v>85</v>
       </c>
       <c r="AF101" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI101" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>85</v>
+        <v>740</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>85</v>
@@ -15859,31 +15865,31 @@
         <v>85</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>593</v>
+        <v>85</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>594</v>
+        <v>138</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS101" t="s" s="2">
-        <v>596</v>
+        <v>85</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>85</v>
+        <v>586</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -15902,19 +15908,19 @@
         <v>85</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>741</v>
+        <v>587</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>742</v>
+        <v>588</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>646</v>
+        <v>589</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>85</v>
@@ -15939,13 +15945,13 @@
         <v>85</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>85</v>
+        <v>591</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>85</v>
@@ -15963,7 +15969,7 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15990,31 +15996,29 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>649</v>
+        <v>594</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS102" t="s" s="2">
-        <v>85</v>
+        <v>596</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>744</v>
-      </c>
+        <v>742</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>85</v>
       </c>
@@ -16023,31 +16027,31 @@
         <v>83</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>643</v>
+        <v>86</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>710</v>
+        <v>743</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>711</v>
+        <v>744</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>712</v>
+        <v>646</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>713</v>
+        <v>647</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>85</v>
@@ -16096,7 +16100,7 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>709</v>
+        <v>742</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16108,7 +16112,7 @@
         <v>85</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>715</v>
+        <v>107</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>85</v>
@@ -16126,10 +16130,10 @@
         <v>85</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>716</v>
+        <v>649</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>717</v>
+        <v>650</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
@@ -16143,9 +16147,11 @@
         <v>745</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="C104" s="2"/>
+        <v>709</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>746</v>
+      </c>
       <c r="D104" t="s" s="2">
         <v>85</v>
       </c>
@@ -16157,25 +16163,29 @@
         <v>95</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>210</v>
+        <v>643</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>154</v>
+        <v>710</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>711</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>713</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>85</v>
       </c>
@@ -16223,19 +16233,19 @@
         <v>85</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>156</v>
+        <v>709</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>85</v>
+        <v>715</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>85</v>
@@ -16253,10 +16263,10 @@
         <v>85</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>85</v>
+        <v>716</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>158</v>
+        <v>717</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>85</v>
@@ -16267,21 +16277,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>85</v>
@@ -16293,17 +16303,15 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>85</v>
@@ -16352,19 +16360,19 @@
         <v>85</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>85</v>
@@ -16396,14 +16404,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>654</v>
+        <v>194</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -16416,26 +16424,24 @@
         <v>85</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>655</v>
+        <v>212</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>656</v>
+        <v>213</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O106" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>85</v>
       </c>
@@ -16483,7 +16489,7 @@
         <v>85</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>657</v>
+        <v>162</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>83</v>
@@ -16516,7 +16522,7 @@
         <v>85</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>85</v>
@@ -16527,45 +16533,45 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>85</v>
+        <v>654</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I107" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>722</v>
+        <v>655</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>723</v>
+        <v>656</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>724</v>
+        <v>197</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>725</v>
+        <v>198</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>85</v>
@@ -16575,7 +16581,7 @@
         <v>85</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>749</v>
+        <v>85</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>85</v>
@@ -16590,13 +16596,13 @@
         <v>85</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>392</v>
+        <v>85</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>85</v>
@@ -16614,22 +16620,22 @@
         <v>85</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>721</v>
+        <v>657</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>750</v>
+        <v>85</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>85</v>
@@ -16641,16 +16647,16 @@
         <v>85</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>726</v>
+        <v>85</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>396</v>
+        <v>85</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>398</v>
+        <v>85</v>
       </c>
       <c r="AS107" t="s" s="2">
         <v>85</v>
@@ -16658,10 +16664,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16669,7 +16675,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>95</v>
@@ -16684,19 +16690,19 @@
         <v>96</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>480</v>
+        <v>172</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>484</v>
+        <v>725</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>85</v>
@@ -16706,7 +16712,7 @@
         <v>85</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>85</v>
+        <v>751</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>85</v>
@@ -16724,41 +16730,43 @@
         <v>228</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>485</v>
+        <v>392</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>486</v>
+        <v>393</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AC108" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD108" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>731</v>
+        <v>85</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>85</v>
+        <v>752</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>85</v>
@@ -16770,31 +16778,29 @@
         <v>85</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>489</v>
+        <v>396</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>490</v>
+        <v>397</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AS108" t="s" s="2">
-        <v>491</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>727</v>
       </c>
-      <c r="C109" t="s" s="2">
-        <v>753</v>
-      </c>
+      <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>85</v>
       </c>
@@ -16815,7 +16821,7 @@
         <v>96</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>172</v>
+        <v>480</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>728</v>
@@ -16864,16 +16870,14 @@
         <v>85</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="AC109" s="2"/>
       <c r="AD109" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>727</v>
@@ -16923,9 +16927,11 @@
         <v>754</v>
       </c>
       <c r="B110" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C110" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>85</v>
       </c>
@@ -16937,25 +16943,29 @@
         <v>95</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>154</v>
+        <v>728</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>85</v>
       </c>
@@ -16979,13 +16989,13 @@
         <v>85</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>85</v>
+        <v>485</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>85</v>
@@ -17003,7 +17013,7 @@
         <v>85</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>156</v>
+        <v>727</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>83</v>
@@ -17012,10 +17022,10 @@
         <v>95</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>85</v>
+        <v>731</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>85</v>
@@ -17030,19 +17040,19 @@
         <v>85</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>85</v>
+        <v>732</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>85</v>
+        <v>489</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>158</v>
+        <v>490</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS110" t="s" s="2">
-        <v>85</v>
+        <v>491</v>
       </c>
     </row>
     <row r="111" hidden="true">
@@ -17054,14 +17064,14 @@
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>85</v>
@@ -17073,17 +17083,15 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>85</v>
@@ -17120,31 +17128,31 @@
         <v>85</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>85</v>
@@ -17183,7 +17191,7 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -17193,29 +17201,27 @@
         <v>84</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>85</v>
       </c>
@@ -17239,29 +17245,31 @@
         <v>85</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>760</v>
+        <v>85</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -17273,16 +17281,16 @@
         <v>85</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>761</v>
+        <v>85</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>85</v>
@@ -17291,10 +17299,10 @@
         <v>85</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>85</v>
@@ -17305,10 +17313,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17319,10 +17327,10 @@
         <v>83</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>85</v>
@@ -17331,19 +17339,19 @@
         <v>96</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>380</v>
+        <v>322</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>85</v>
@@ -17368,13 +17376,11 @@
         <v>85</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>85</v>
+        <v>762</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>85</v>
@@ -17392,13 +17398,13 @@
         <v>85</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>85</v>
@@ -17407,13 +17413,13 @@
         <v>107</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>85</v>
+        <v>763</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>85</v>
@@ -17422,10 +17428,10 @@
         <v>85</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>384</v>
+        <v>326</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>385</v>
+        <v>327</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>85</v>
@@ -17439,7 +17445,7 @@
         <v>764</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>733</v>
+        <v>765</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17453,28 +17459,28 @@
         <v>95</v>
       </c>
       <c r="H114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J114" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K114" t="s" s="2">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>734</v>
+        <v>379</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>735</v>
+        <v>380</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>736</v>
+        <v>381</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>579</v>
+        <v>382</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>85</v>
@@ -17499,13 +17505,13 @@
         <v>85</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>85</v>
@@ -17523,7 +17529,7 @@
         <v>85</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>733</v>
+        <v>383</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>83</v>
@@ -17532,7 +17538,7 @@
         <v>95</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>737</v>
+        <v>85</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>107</v>
@@ -17553,10 +17559,10 @@
         <v>85</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>584</v>
+        <v>385</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>85</v>
@@ -17567,24 +17573,24 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>586</v>
+        <v>85</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>85</v>
@@ -17596,16 +17602,16 @@
         <v>172</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>587</v>
+        <v>736</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>588</v>
+        <v>737</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>589</v>
+        <v>738</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>85</v>
@@ -17633,10 +17639,10 @@
         <v>228</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>85</v>
@@ -17654,16 +17660,16 @@
         <v>85</v>
       </c>
       <c r="AF115" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI115" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>107</v>
@@ -17681,31 +17687,31 @@
         <v>85</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>593</v>
+        <v>85</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>594</v>
+        <v>138</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS115" t="s" s="2">
-        <v>596</v>
+        <v>85</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>85</v>
+        <v>586</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -17724,19 +17730,19 @@
         <v>85</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>741</v>
+        <v>587</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>742</v>
+        <v>588</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>646</v>
+        <v>589</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>85</v>
@@ -17761,13 +17767,13 @@
         <v>85</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>85</v>
+        <v>591</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>85</v>
@@ -17785,7 +17791,7 @@
         <v>85</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -17812,31 +17818,29 @@
         <v>85</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>649</v>
+        <v>594</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS116" t="s" s="2">
-        <v>85</v>
+        <v>596</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>768</v>
-      </c>
+        <v>742</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>85</v>
       </c>
@@ -17845,31 +17849,31 @@
         <v>83</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>643</v>
+        <v>86</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>710</v>
+        <v>743</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>711</v>
+        <v>744</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>712</v>
+        <v>646</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>713</v>
+        <v>647</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>85</v>
@@ -17918,7 +17922,7 @@
         <v>85</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>709</v>
+        <v>742</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>83</v>
@@ -17930,7 +17934,7 @@
         <v>85</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>715</v>
+        <v>107</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>85</v>
@@ -17948,10 +17952,10 @@
         <v>85</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>716</v>
+        <v>649</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>717</v>
+        <v>650</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>85</v>
@@ -17965,9 +17969,11 @@
         <v>769</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>709</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>770</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>85</v>
       </c>
@@ -17979,25 +17985,29 @@
         <v>95</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>210</v>
+        <v>643</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>154</v>
+        <v>710</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>711</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>713</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>85</v>
       </c>
@@ -18045,19 +18055,19 @@
         <v>85</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>156</v>
+        <v>709</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>85</v>
+        <v>715</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>85</v>
@@ -18075,10 +18085,10 @@
         <v>85</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>85</v>
+        <v>716</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>158</v>
+        <v>717</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>85</v>
@@ -18089,21 +18099,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>85</v>
@@ -18115,17 +18125,15 @@
         <v>85</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>85</v>
@@ -18174,19 +18182,19 @@
         <v>85</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>85</v>
@@ -18218,14 +18226,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>654</v>
+        <v>194</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -18238,26 +18246,24 @@
         <v>85</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K120" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>655</v>
+        <v>212</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>656</v>
+        <v>213</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O120" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>85</v>
       </c>
@@ -18305,7 +18311,7 @@
         <v>85</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>657</v>
+        <v>162</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>83</v>
@@ -18338,7 +18344,7 @@
         <v>85</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>85</v>
@@ -18349,45 +18355,45 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>85</v>
+        <v>654</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I121" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J121" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>722</v>
+        <v>655</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>723</v>
+        <v>656</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>724</v>
+        <v>197</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>725</v>
+        <v>198</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>85</v>
@@ -18397,7 +18403,7 @@
         <v>85</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>749</v>
+        <v>85</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>85</v>
@@ -18412,13 +18418,13 @@
         <v>85</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>392</v>
+        <v>85</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>85</v>
@@ -18436,22 +18442,22 @@
         <v>85</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>721</v>
+        <v>657</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>773</v>
+        <v>85</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>85</v>
@@ -18463,16 +18469,16 @@
         <v>85</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>726</v>
+        <v>85</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>396</v>
+        <v>85</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>398</v>
+        <v>85</v>
       </c>
       <c r="AS121" t="s" s="2">
         <v>85</v>
@@ -18483,7 +18489,7 @@
         <v>774</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18491,7 +18497,7 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>95</v>
@@ -18506,19 +18512,19 @@
         <v>96</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>480</v>
+        <v>172</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>484</v>
+        <v>725</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>85</v>
@@ -18528,7 +18534,7 @@
         <v>85</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>85</v>
+        <v>751</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>85</v>
@@ -18546,41 +18552,43 @@
         <v>228</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>485</v>
+        <v>392</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>486</v>
+        <v>393</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AC122" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>731</v>
+        <v>85</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>85</v>
+        <v>775</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>85</v>
@@ -18592,31 +18600,29 @@
         <v>85</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>489</v>
+        <v>396</v>
       </c>
       <c r="AQ122" t="s" s="2">
-        <v>490</v>
+        <v>397</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AS122" t="s" s="2">
-        <v>491</v>
+        <v>85</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>727</v>
       </c>
-      <c r="C123" t="s" s="2">
-        <v>753</v>
-      </c>
+      <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>85</v>
       </c>
@@ -18637,7 +18643,7 @@
         <v>96</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>172</v>
+        <v>480</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>728</v>
@@ -18686,16 +18692,14 @@
         <v>85</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="AC123" s="2"/>
       <c r="AD123" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF123" t="s" s="2">
         <v>727</v>
@@ -18742,12 +18746,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B124" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C124" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>85</v>
       </c>
@@ -18759,25 +18765,29 @@
         <v>95</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>154</v>
+        <v>728</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>85</v>
       </c>
@@ -18801,13 +18811,13 @@
         <v>85</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>85</v>
+        <v>485</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>85</v>
@@ -18825,7 +18835,7 @@
         <v>85</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>156</v>
+        <v>727</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>83</v>
@@ -18834,10 +18844,10 @@
         <v>95</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>85</v>
+        <v>731</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>85</v>
@@ -18852,38 +18862,38 @@
         <v>85</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>85</v>
+        <v>732</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>85</v>
+        <v>489</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>158</v>
+        <v>490</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS124" t="s" s="2">
-        <v>85</v>
+        <v>491</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>757</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>85</v>
@@ -18895,17 +18905,15 @@
         <v>85</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>85</v>
@@ -18942,31 +18950,31 @@
         <v>85</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>85</v>
@@ -18998,14 +19006,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>759</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -19015,29 +19023,27 @@
         <v>84</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>85</v>
       </c>
@@ -19061,29 +19067,31 @@
         <v>85</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y126" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z126" t="s" s="2">
-        <v>779</v>
+        <v>85</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -19095,16 +19103,16 @@
         <v>85</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>780</v>
+        <v>85</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>85</v>
@@ -19113,10 +19121,10 @@
         <v>85</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>85</v>
@@ -19127,10 +19135,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19141,10 +19149,10 @@
         <v>83</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>85</v>
@@ -19153,19 +19161,19 @@
         <v>96</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>380</v>
+        <v>322</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>85</v>
@@ -19190,13 +19198,11 @@
         <v>85</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>85</v>
+        <v>781</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>85</v>
@@ -19214,13 +19220,13 @@
         <v>85</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>85</v>
@@ -19229,13 +19235,13 @@
         <v>107</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>85</v>
+        <v>782</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>85</v>
@@ -19244,10 +19250,10 @@
         <v>85</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>384</v>
+        <v>326</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>385</v>
+        <v>327</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>85</v>
@@ -19258,10 +19264,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>733</v>
+        <v>765</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19275,28 +19281,28 @@
         <v>95</v>
       </c>
       <c r="H128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J128" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I128" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K128" t="s" s="2">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>734</v>
+        <v>379</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>735</v>
+        <v>380</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>736</v>
+        <v>381</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>579</v>
+        <v>382</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>85</v>
@@ -19321,13 +19327,13 @@
         <v>85</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>85</v>
@@ -19345,7 +19351,7 @@
         <v>85</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>733</v>
+        <v>383</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -19354,7 +19360,7 @@
         <v>95</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>737</v>
+        <v>85</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>107</v>
@@ -19375,10 +19381,10 @@
         <v>85</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>584</v>
+        <v>385</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>85</v>
@@ -19389,24 +19395,24 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>586</v>
+        <v>85</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>85</v>
@@ -19418,16 +19424,16 @@
         <v>172</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>587</v>
+        <v>736</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>588</v>
+        <v>737</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>589</v>
+        <v>738</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>85</v>
@@ -19455,10 +19461,10 @@
         <v>228</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>85</v>
@@ -19476,16 +19482,16 @@
         <v>85</v>
       </c>
       <c r="AF129" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI129" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>107</v>
@@ -19503,31 +19509,31 @@
         <v>85</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>593</v>
+        <v>85</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>594</v>
+        <v>138</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS129" t="s" s="2">
-        <v>596</v>
+        <v>85</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>85</v>
+        <v>586</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -19546,19 +19552,19 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>741</v>
+        <v>587</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>742</v>
+        <v>588</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>646</v>
+        <v>589</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>85</v>
@@ -19583,13 +19589,13 @@
         <v>85</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>85</v>
+        <v>591</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>85</v>
@@ -19607,7 +19613,7 @@
         <v>85</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>83</v>
@@ -19634,23 +19640,154 @@
         <v>85</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AP130" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AQ130" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AR130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS130" t="s" s="2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP131" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="AQ130" t="s" s="2">
+      <c r="AQ131" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AR130" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS130" t="s" s="2">
+      <c r="AR131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS131" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS130">
+  <autoFilter ref="A1:AS131">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19660,7 +19797,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI129">
+  <conditionalFormatting sqref="A2:AI130">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5434" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5434" uniqueCount="788">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -792,7 +792,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
+    <t>660: source value based on GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -925,10 +925,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vs-10-655:120.5-4: if null then #final {null}vs-10-656:120.5-4: if not null then #entered-in-error {null}</t>
-  </si>
-  <si>
-    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
+vs-10-655:If (120.5-4) is null then fixed value #final {null}vs-10-656:If (120.5-4) is not null then fixed value #entered-in-error {null}</t>
+  </si>
+  <si>
+    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) if not null</t>
   </si>
   <si>
     <t>Observation.Extension[ObservationExtension].Removed</t>
@@ -1301,7 +1301,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
+    <t>659: reference based on GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
     <t>Vital.VitalSign.PatientIEN</t>
@@ -1430,7 +1430,7 @@
 </t>
   </si>
   <si>
-    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
+    <t>657: source value based on GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
@@ -1455,7 +1455,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
+    <t>652: source value based on GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
@@ -1486,7 +1486,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
+    <t>1653: reference based on GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
   </si>
   <si>
     <t>Vital.VitalSign.LocationIEN</t>
@@ -1595,7 +1595,11 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID not = 4500634</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vs-10-664:If VUID not = 4500634 then source value from (120.5-1.2) {null}</t>
+  </si>
+  <si>
+    <t>664: source value based on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) if VUID not = 4500634</t>
   </si>
   <si>
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
@@ -10815,16 +10819,16 @@
         <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>107</v>
+        <v>507</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>85</v>
@@ -10833,10 +10837,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10847,10 +10851,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10876,20 +10880,20 @@
         <v>115</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>85</v>
@@ -10913,10 +10917,10 @@
         <v>175</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10934,7 +10938,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10964,10 +10968,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10978,10 +10982,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11007,14 +11011,14 @@
         <v>210</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -11063,7 +11067,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -11093,10 +11097,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -11107,10 +11111,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11136,14 +11140,14 @@
         <v>109</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -11192,7 +11196,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -11201,7 +11205,7 @@
         <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>107</v>
@@ -11222,10 +11226,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -11236,10 +11240,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11265,16 +11269,16 @@
         <v>115</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -11323,7 +11327,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -11338,7 +11342,7 @@
         <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>405</v>
@@ -11353,10 +11357,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11367,10 +11371,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11396,10 +11400,10 @@
         <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11494,10 +11498,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11619,13 +11623,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>85</v>
@@ -11647,16 +11651,16 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11750,10 +11754,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11877,10 +11881,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12004,10 +12008,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12047,7 +12051,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>85</v>
@@ -12133,10 +12137,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12159,7 +12163,7 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>173</v>
@@ -12177,7 +12181,7 @@
         <v>85</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>85</v>
@@ -12260,10 +12264,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12289,10 +12293,10 @@
         <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12343,7 +12347,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12387,10 +12391,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12416,16 +12420,16 @@
         <v>172</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12453,10 +12457,10 @@
         <v>228</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12474,7 +12478,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12483,13 +12487,13 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>85</v>
@@ -12507,7 +12511,7 @@
         <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12518,14 +12522,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12547,16 +12551,16 @@
         <v>172</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12584,10 +12588,10 @@
         <v>228</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12605,7 +12609,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12632,27 +12636,27 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12675,19 +12679,19 @@
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12736,7 +12740,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12766,10 +12770,10 @@
         <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -12780,10 +12784,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12809,13 +12813,13 @@
         <v>172</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12845,7 +12849,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>85</v>
@@ -12863,7 +12867,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12878,7 +12882,7 @@
         <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>85</v>
@@ -12890,27 +12894,27 @@
         <v>85</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS78" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12936,16 +12940,16 @@
         <v>172</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
@@ -12974,7 +12978,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>85</v>
@@ -12992,7 +12996,7 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -13007,7 +13011,7 @@
         <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>85</v>
@@ -13022,10 +13026,10 @@
         <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
@@ -13036,10 +13040,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13062,16 +13066,16 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -13121,7 +13125,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13148,27 +13152,27 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS80" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13191,16 +13195,16 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13250,7 +13254,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -13277,27 +13281,27 @@
         <v>85</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS81" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13320,19 +13324,19 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13381,7 +13385,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13393,7 +13397,7 @@
         <v>85</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>85</v>
@@ -13411,10 +13415,10 @@
         <v>85</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
@@ -13425,10 +13429,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13552,10 +13556,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13681,14 +13685,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13710,10 +13714,10 @@
         <v>140</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>197</v>
@@ -13768,7 +13772,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13812,10 +13816,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13838,13 +13842,13 @@
         <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13895,7 +13899,7 @@
         <v>85</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -13904,7 +13908,7 @@
         <v>95</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>107</v>
@@ -13925,10 +13929,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -13939,10 +13943,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13965,13 +13969,13 @@
         <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14022,7 +14026,7 @@
         <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -14031,7 +14035,7 @@
         <v>95</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>107</v>
@@ -14052,10 +14056,10 @@
         <v>85</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>85</v>
@@ -14066,10 +14070,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14095,16 +14099,16 @@
         <v>172</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
@@ -14132,10 +14136,10 @@
         <v>119</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>85</v>
@@ -14153,7 +14157,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14180,13 +14184,13 @@
         <v>85</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -14197,10 +14201,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14226,16 +14230,16 @@
         <v>172</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>85</v>
@@ -14260,13 +14264,13 @@
         <v>85</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>85</v>
@@ -14284,7 +14288,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14311,13 +14315,13 @@
         <v>85</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -14328,10 +14332,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14354,17 +14358,17 @@
         <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14413,7 +14417,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14446,7 +14450,7 @@
         <v>85</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
@@ -14457,10 +14461,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14486,10 +14490,10 @@
         <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14540,7 +14544,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14570,10 +14574,10 @@
         <v>85</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14584,10 +14588,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14610,16 +14614,16 @@
         <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14669,7 +14673,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14699,10 +14703,10 @@
         <v>85</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
@@ -14713,10 +14717,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14739,16 +14743,16 @@
         <v>96</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14798,7 +14802,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -14828,10 +14832,10 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
@@ -14842,10 +14846,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14868,19 +14872,19 @@
         <v>96</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -14917,7 +14921,7 @@
         <v>85</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14927,7 +14931,7 @@
         <v>144</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14939,7 +14943,7 @@
         <v>85</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>85</v>
@@ -14957,10 +14961,10 @@
         <v>85</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
@@ -14971,10 +14975,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15098,10 +15102,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15227,14 +15231,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -15256,10 +15260,10 @@
         <v>140</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>197</v>
@@ -15314,7 +15318,7 @@
         <v>85</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15358,10 +15362,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15387,16 +15391,16 @@
         <v>172</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>85</v>
@@ -15445,7 +15449,7 @@
         <v>85</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>95</v>
@@ -15472,7 +15476,7 @@
         <v>85</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>396</v>
@@ -15489,10 +15493,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15518,13 +15522,13 @@
         <v>480</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>484</v>
@@ -15574,7 +15578,7 @@
         <v>144</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15583,7 +15587,7 @@
         <v>95</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>107</v>
@@ -15601,7 +15605,7 @@
         <v>85</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>489</v>
@@ -15618,10 +15622,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>493</v>
@@ -15649,13 +15653,13 @@
         <v>494</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>484</v>
@@ -15707,7 +15711,7 @@
         <v>85</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15716,13 +15720,13 @@
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>85</v>
@@ -15734,7 +15738,7 @@
         <v>85</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>489</v>
@@ -15751,10 +15755,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15780,16 +15784,16 @@
         <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>85</v>
@@ -15817,10 +15821,10 @@
         <v>228</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>85</v>
@@ -15838,7 +15842,7 @@
         <v>85</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15847,13 +15851,13 @@
         <v>95</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>85</v>
@@ -15871,7 +15875,7 @@
         <v>138</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>85</v>
@@ -15882,14 +15886,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -15911,16 +15915,16 @@
         <v>172</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>85</v>
@@ -15948,10 +15952,10 @@
         <v>228</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>85</v>
@@ -15969,7 +15973,7 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15996,27 +16000,27 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS102" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16042,16 +16046,16 @@
         <v>86</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>85</v>
@@ -16100,7 +16104,7 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16130,10 +16134,10 @@
         <v>85</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
@@ -16144,13 +16148,13 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>85</v>
@@ -16172,19 +16176,19 @@
         <v>96</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>85</v>
@@ -16233,7 +16237,7 @@
         <v>85</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -16245,7 +16249,7 @@
         <v>85</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>85</v>
@@ -16263,10 +16267,10 @@
         <v>85</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>85</v>
@@ -16277,10 +16281,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16404,10 +16408,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16533,14 +16537,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -16562,10 +16566,10 @@
         <v>140</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>197</v>
@@ -16620,7 +16624,7 @@
         <v>85</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -16664,10 +16668,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16693,16 +16697,16 @@
         <v>172</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>85</v>
@@ -16712,7 +16716,7 @@
         <v>85</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>85</v>
@@ -16751,7 +16755,7 @@
         <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>95</v>
@@ -16766,7 +16770,7 @@
         <v>107</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>85</v>
@@ -16778,7 +16782,7 @@
         <v>85</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>396</v>
@@ -16795,10 +16799,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16824,13 +16828,13 @@
         <v>480</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>484</v>
@@ -16880,7 +16884,7 @@
         <v>144</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>83</v>
@@ -16889,7 +16893,7 @@
         <v>95</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>107</v>
@@ -16907,7 +16911,7 @@
         <v>85</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>489</v>
@@ -16924,13 +16928,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>85</v>
@@ -16955,13 +16959,13 @@
         <v>172</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>484</v>
@@ -17013,7 +17017,7 @@
         <v>85</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>83</v>
@@ -17022,7 +17026,7 @@
         <v>95</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>107</v>
@@ -17040,7 +17044,7 @@
         <v>85</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>489</v>
@@ -17057,10 +17061,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17184,10 +17188,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17313,10 +17317,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17380,7 +17384,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>85</v>
@@ -17413,7 +17417,7 @@
         <v>107</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>85</v>
@@ -17442,10 +17446,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17573,10 +17577,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17602,16 +17606,16 @@
         <v>172</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>85</v>
@@ -17639,10 +17643,10 @@
         <v>228</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>85</v>
@@ -17660,7 +17664,7 @@
         <v>85</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
@@ -17669,7 +17673,7 @@
         <v>95</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>107</v>
@@ -17693,7 +17697,7 @@
         <v>138</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>85</v>
@@ -17704,14 +17708,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -17733,16 +17737,16 @@
         <v>172</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>85</v>
@@ -17770,10 +17774,10 @@
         <v>228</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>85</v>
@@ -17791,7 +17795,7 @@
         <v>85</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -17818,27 +17822,27 @@
         <v>85</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS116" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17864,16 +17868,16 @@
         <v>86</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>85</v>
@@ -17922,7 +17926,7 @@
         <v>85</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>83</v>
@@ -17952,10 +17956,10 @@
         <v>85</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>85</v>
@@ -17966,13 +17970,13 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>85</v>
@@ -17994,19 +17998,19 @@
         <v>96</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>85</v>
@@ -18055,7 +18059,7 @@
         <v>85</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>83</v>
@@ -18067,7 +18071,7 @@
         <v>85</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>85</v>
@@ -18085,10 +18089,10 @@
         <v>85</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>85</v>
@@ -18099,10 +18103,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18226,10 +18230,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18355,14 +18359,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -18384,10 +18388,10 @@
         <v>140</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>197</v>
@@ -18442,7 +18446,7 @@
         <v>85</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>83</v>
@@ -18486,10 +18490,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18515,16 +18519,16 @@
         <v>172</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>85</v>
@@ -18534,7 +18538,7 @@
         <v>85</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>85</v>
@@ -18573,7 +18577,7 @@
         <v>85</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>95</v>
@@ -18588,7 +18592,7 @@
         <v>107</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>85</v>
@@ -18600,7 +18604,7 @@
         <v>85</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>396</v>
@@ -18617,10 +18621,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18646,13 +18650,13 @@
         <v>480</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>484</v>
@@ -18702,7 +18706,7 @@
         <v>144</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>83</v>
@@ -18711,7 +18715,7 @@
         <v>95</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>107</v>
@@ -18729,7 +18733,7 @@
         <v>85</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>489</v>
@@ -18746,13 +18750,13 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>85</v>
@@ -18777,13 +18781,13 @@
         <v>172</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>484</v>
@@ -18835,7 +18839,7 @@
         <v>85</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>83</v>
@@ -18844,7 +18848,7 @@
         <v>95</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>107</v>
@@ -18862,7 +18866,7 @@
         <v>85</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>489</v>
@@ -18879,10 +18883,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19006,10 +19010,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19135,10 +19139,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19202,7 +19206,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>85</v>
@@ -19235,7 +19239,7 @@
         <v>107</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>85</v>
@@ -19264,10 +19268,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19395,10 +19399,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19424,16 +19428,16 @@
         <v>172</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>85</v>
@@ -19461,10 +19465,10 @@
         <v>228</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>85</v>
@@ -19482,7 +19486,7 @@
         <v>85</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>83</v>
@@ -19491,7 +19495,7 @@
         <v>95</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>107</v>
@@ -19515,7 +19519,7 @@
         <v>138</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>85</v>
@@ -19526,14 +19530,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -19555,16 +19559,16 @@
         <v>172</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>85</v>
@@ -19592,10 +19596,10 @@
         <v>228</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>85</v>
@@ -19613,7 +19617,7 @@
         <v>85</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>83</v>
@@ -19640,27 +19644,27 @@
         <v>85</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS130" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19686,16 +19690,16 @@
         <v>86</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>85</v>
@@ -19744,7 +19748,7 @@
         <v>85</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>83</v>
@@ -19774,10 +19778,10 @@
         <v>85</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5119" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5119" uniqueCount="769">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -931,7 +931,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vs-10-655:If (120.5-4) is null then fixed value #final {null}vs-10-656:If (120.5-4) is not null then fixed value #entered-in-error {null}</t>
+vs-10-655:If (120.5-4) is null then fixed value #final {true}vs-10-656:If (120.5-4) is not null then fixed value #entered-in-error {true}</t>
   </si>
   <si>
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) if not null</t>
@@ -1279,10 +1279,11 @@
     <t>http://va.gov/fhir/ValueSet/VitalsCodes</t>
   </si>
   <si>
-    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
-  </si>
-  <si>
-    <t>Vital.VitalSign.VitalTypeIEN</t>
+    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE &gt; GMRV VITAL TYPE - VUID (120.5-.03 &gt; 120.51-99.99)</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.VitalTypeIEN
+Dim.VitalType.VUID</t>
   </si>
   <si>
     <t>Observation.ObservationCode,Observation.Extension[ObservationExtension].BMI</t>
@@ -1605,7 +1606,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vs-10-664:If VUID not = 4500634 then source value from (120.5-1.2) {null}</t>
+vs-10-664:If VUID not = 4500634 then source value from (120.5-1.2) {true}</t>
   </si>
   <si>
     <t>664: source value based on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) if VUID not = 4500634</t>
@@ -1727,6 +1728,9 @@
   </si>
   <si>
     <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.VitalTypeIEN</t>
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
@@ -11289,7 +11293,7 @@
         <v>550</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>408</v>
+        <v>551</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>409</v>
@@ -11304,7 +11308,7 @@
         <v>533</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11315,10 +11319,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11344,16 +11348,16 @@
         <v>172</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>85</v>
@@ -11381,10 +11385,10 @@
         <v>230</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>85</v>
@@ -11402,7 +11406,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11411,13 +11415,13 @@
         <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>85</v>
@@ -11435,7 +11439,7 @@
         <v>138</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11446,14 +11450,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -11475,16 +11479,16 @@
         <v>172</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11512,10 +11516,10 @@
         <v>230</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>85</v>
@@ -11533,7 +11537,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11560,27 +11564,27 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS68" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11603,19 +11607,19 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11664,7 +11668,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11694,10 +11698,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11708,10 +11712,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11737,13 +11741,13 @@
         <v>172</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11772,10 +11776,10 @@
         <v>175</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11793,7 +11797,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11808,7 +11812,7 @@
         <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>85</v>
@@ -11820,27 +11824,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11866,16 +11870,16 @@
         <v>172</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11903,10 +11907,10 @@
         <v>175</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11924,7 +11928,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11939,7 +11943,7 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>85</v>
@@ -11954,10 +11958,10 @@
         <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11968,10 +11972,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11994,16 +11998,16 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -12053,7 +12057,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -12080,27 +12084,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12123,16 +12127,16 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -12182,7 +12186,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -12209,27 +12213,27 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12252,19 +12256,19 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -12313,7 +12317,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12325,7 +12329,7 @@
         <v>85</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>85</v>
@@ -12343,10 +12347,10 @@
         <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
@@ -12357,10 +12361,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12484,10 +12488,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12613,14 +12617,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12642,10 +12646,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>199</v>
@@ -12700,7 +12704,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12744,10 +12748,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12770,13 +12774,13 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12827,7 +12831,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12836,7 +12840,7 @@
         <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>107</v>
@@ -12857,10 +12861,10 @@
         <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12871,10 +12875,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12897,13 +12901,13 @@
         <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12954,7 +12958,7 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12963,7 +12967,7 @@
         <v>95</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>107</v>
@@ -12984,10 +12988,10 @@
         <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
@@ -12998,10 +13002,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13027,16 +13031,16 @@
         <v>172</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -13064,10 +13068,10 @@
         <v>119</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>85</v>
@@ -13085,7 +13089,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13112,13 +13116,13 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
@@ -13129,10 +13133,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13158,16 +13162,16 @@
         <v>172</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>85</v>
@@ -13192,13 +13196,13 @@
         <v>85</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>85</v>
@@ -13216,7 +13220,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -13243,13 +13247,13 @@
         <v>85</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
@@ -13260,10 +13264,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13286,17 +13290,17 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13345,7 +13349,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13378,7 +13382,7 @@
         <v>85</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
@@ -13389,10 +13393,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13418,10 +13422,10 @@
         <v>212</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13472,7 +13476,7 @@
         <v>85</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13502,10 +13506,10 @@
         <v>85</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>85</v>
@@ -13516,10 +13520,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13542,16 +13546,16 @@
         <v>96</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13601,7 +13605,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13631,10 +13635,10 @@
         <v>85</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
@@ -13645,10 +13649,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13671,16 +13675,16 @@
         <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13730,7 +13734,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13760,10 +13764,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13774,10 +13778,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13800,19 +13804,19 @@
         <v>96</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>85</v>
@@ -13849,7 +13853,7 @@
         <v>85</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AC86" s="2"/>
       <c r="AD86" t="s" s="2">
@@ -13859,7 +13863,7 @@
         <v>144</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -13871,7 +13875,7 @@
         <v>85</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>85</v>
@@ -13889,10 +13893,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -13903,10 +13907,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14030,10 +14034,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14159,14 +14163,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -14188,10 +14192,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>199</v>
@@ -14246,7 +14250,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14290,10 +14294,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14319,16 +14323,16 @@
         <v>172</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14377,7 +14381,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>95</v>
@@ -14404,7 +14408,7 @@
         <v>85</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>398</v>
@@ -14421,10 +14425,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14450,13 +14454,13 @@
         <v>483</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>487</v>
@@ -14506,7 +14510,7 @@
         <v>144</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14515,7 +14519,7 @@
         <v>95</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>107</v>
@@ -14533,7 +14537,7 @@
         <v>85</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>492</v>
@@ -14550,10 +14554,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>496</v>
@@ -14581,13 +14585,13 @@
         <v>497</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>487</v>
@@ -14639,7 +14643,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14648,13 +14652,13 @@
         <v>95</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>85</v>
@@ -14666,7 +14670,7 @@
         <v>85</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>492</v>
@@ -14683,10 +14687,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14712,16 +14716,16 @@
         <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14749,10 +14753,10 @@
         <v>230</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>85</v>
@@ -14770,7 +14774,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -14779,13 +14783,13 @@
         <v>95</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>85</v>
@@ -14803,7 +14807,7 @@
         <v>138</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
@@ -14814,14 +14818,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -14843,16 +14847,16 @@
         <v>172</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -14880,10 +14884,10 @@
         <v>230</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>85</v>
@@ -14901,7 +14905,7 @@
         <v>85</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14928,27 +14932,27 @@
         <v>85</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS94" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14974,16 +14978,16 @@
         <v>86</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>85</v>
@@ -15032,7 +15036,7 @@
         <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -15062,10 +15066,10 @@
         <v>85</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
@@ -15076,13 +15080,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>85</v>
@@ -15104,19 +15108,19 @@
         <v>96</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>85</v>
@@ -15165,7 +15169,7 @@
         <v>85</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15177,7 +15181,7 @@
         <v>85</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>85</v>
@@ -15195,10 +15199,10 @@
         <v>85</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>85</v>
@@ -15209,10 +15213,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15336,10 +15340,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15465,14 +15469,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15494,10 +15498,10 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>199</v>
@@ -15552,7 +15556,7 @@
         <v>85</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15596,10 +15600,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15625,16 +15629,16 @@
         <v>172</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>85</v>
@@ -15644,7 +15648,7 @@
         <v>85</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>85</v>
@@ -15683,7 +15687,7 @@
         <v>85</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>95</v>
@@ -15698,7 +15702,7 @@
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>85</v>
@@ -15710,7 +15714,7 @@
         <v>85</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>398</v>
@@ -15727,10 +15731,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15756,13 +15760,13 @@
         <v>483</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>487</v>
@@ -15812,7 +15816,7 @@
         <v>144</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15821,7 +15825,7 @@
         <v>95</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>107</v>
@@ -15839,7 +15843,7 @@
         <v>85</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>492</v>
@@ -15856,13 +15860,13 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>85</v>
@@ -15887,13 +15891,13 @@
         <v>172</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>487</v>
@@ -15945,7 +15949,7 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15954,7 +15958,7 @@
         <v>95</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>107</v>
@@ -15972,7 +15976,7 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>492</v>
@@ -15989,10 +15993,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16116,10 +16120,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16245,10 +16249,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16311,10 +16315,10 @@
         <v>175</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>85</v>
@@ -16347,7 +16351,7 @@
         <v>107</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>85</v>
@@ -16376,10 +16380,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16507,10 +16511,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16536,16 +16540,16 @@
         <v>172</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>85</v>
@@ -16573,10 +16577,10 @@
         <v>230</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>85</v>
@@ -16594,7 +16598,7 @@
         <v>85</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -16603,7 +16607,7 @@
         <v>95</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>107</v>
@@ -16627,7 +16631,7 @@
         <v>138</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>85</v>
@@ -16638,14 +16642,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -16667,16 +16671,16 @@
         <v>172</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>85</v>
@@ -16704,10 +16708,10 @@
         <v>230</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>85</v>
@@ -16725,7 +16729,7 @@
         <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>83</v>
@@ -16752,27 +16756,27 @@
         <v>85</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16798,16 +16802,16 @@
         <v>86</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>85</v>
@@ -16856,7 +16860,7 @@
         <v>85</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>83</v>
@@ -16886,10 +16890,10 @@
         <v>85</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AR109" t="s" s="2">
         <v>85</v>
@@ -16900,13 +16904,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>85</v>
@@ -16928,19 +16932,19 @@
         <v>96</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>85</v>
@@ -16989,7 +16993,7 @@
         <v>85</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>83</v>
@@ -17001,7 +17005,7 @@
         <v>85</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>85</v>
@@ -17019,10 +17023,10 @@
         <v>85</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>85</v>
@@ -17033,10 +17037,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17160,10 +17164,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17289,14 +17293,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -17318,10 +17322,10 @@
         <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>199</v>
@@ -17376,7 +17380,7 @@
         <v>85</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
@@ -17420,10 +17424,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17449,16 +17453,16 @@
         <v>172</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>85</v>
@@ -17468,7 +17472,7 @@
         <v>85</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>85</v>
@@ -17507,7 +17511,7 @@
         <v>85</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>95</v>
@@ -17522,7 +17526,7 @@
         <v>107</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>85</v>
@@ -17534,7 +17538,7 @@
         <v>85</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>398</v>
@@ -17551,10 +17555,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17580,13 +17584,13 @@
         <v>483</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O115" t="s" s="2">
         <v>487</v>
@@ -17636,7 +17640,7 @@
         <v>144</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
@@ -17645,7 +17649,7 @@
         <v>95</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>107</v>
@@ -17663,7 +17667,7 @@
         <v>85</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>492</v>
@@ -17680,13 +17684,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>85</v>
@@ -17711,13 +17715,13 @@
         <v>172</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O116" t="s" s="2">
         <v>487</v>
@@ -17769,7 +17773,7 @@
         <v>85</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -17778,7 +17782,7 @@
         <v>95</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>107</v>
@@ -17796,7 +17800,7 @@
         <v>85</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>492</v>
@@ -17813,10 +17817,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17940,10 +17944,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18069,10 +18073,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18135,10 +18139,10 @@
         <v>175</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>85</v>
@@ -18171,7 +18175,7 @@
         <v>107</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>85</v>
@@ -18200,10 +18204,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18331,10 +18335,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18360,16 +18364,16 @@
         <v>172</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>85</v>
@@ -18397,10 +18401,10 @@
         <v>230</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>85</v>
@@ -18418,7 +18422,7 @@
         <v>85</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>83</v>
@@ -18427,7 +18431,7 @@
         <v>95</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>107</v>
@@ -18451,7 +18455,7 @@
         <v>138</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>85</v>
@@ -18462,14 +18466,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -18491,16 +18495,16 @@
         <v>172</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>85</v>
@@ -18528,10 +18532,10 @@
         <v>230</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>85</v>
@@ -18549,7 +18553,7 @@
         <v>85</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -18576,27 +18580,27 @@
         <v>85</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AQ122" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AR122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS122" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18622,16 +18626,16 @@
         <v>86</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>85</v>
@@ -18680,7 +18684,7 @@
         <v>85</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>83</v>
@@ -18710,10 +18714,10 @@
         <v>85</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5119" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4747" uniqueCount="753">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -968,6 +968,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t>value:coding.code}
+value:coding.system}</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:VSCat</t>
+  </si>
+  <si>
+    <t>VSCat</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -978,29 +1000,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t>value:coding.code}
-value:coding.system}</t>
-  </si>
-  <si>
     <t>658: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#vital-signs</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat</t>
-  </si>
-  <si>
-    <t>VSCat</t>
   </si>
   <si>
     <t>Observation.category:VSCat.id</t>
@@ -1760,9 +1760,6 @@
   <si>
     <t>obs-6
 vs-2</t>
-  </si>
-  <si>
-    <t>1793: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2242,12 +2239,6 @@
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>2193: target not supported</t>
-  </si>
-  <si>
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
@@ -2263,9 +2254,6 @@
   <si>
     <t>obs-6
 vs-3</t>
-  </si>
-  <si>
-    <t>1794: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2319,24 +2307,6 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].coding</t>
-  </si>
-  <si>
     <t>see mapping [VF_VitalsPrecondition](ConceptMap-VF-VitalsPrecondition.html)</t>
   </si>
   <si>
@@ -2346,12 +2316,6 @@
     <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
-    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].text</t>
-  </si>
-  <si>
     <t>Observation.component:va-pre-condition.dataAbsentReason</t>
   </si>
   <si>
@@ -2388,15 +2352,6 @@
     <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept</t>
   </si>
   <si>
-    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
     <t>see mapping [VF_VitalsQualifyingDevice](ConceptMap-VF-VitalsQualifyingDevice.html)</t>
   </si>
   <si>
@@ -2404,9 +2359,6 @@
   </si>
   <si>
     <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.text</t>
   </si>
   <si>
     <t>Observation.component:va-pre-condition-device.dataAbsentReason</t>
@@ -2732,10 +2684,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS123"/>
+  <dimension ref="A1:AS114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="85.0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="75.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.28515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -6953,7 +6905,7 @@
         <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>307</v>
+        <v>85</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>85</v>
@@ -6971,16 +6923,16 @@
         <v>119</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB33" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -7005,28 +6957,28 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AR33" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AR33" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AS33" t="s" s="2">
         <v>85</v>
@@ -7034,13 +6986,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>302</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>85</v>
@@ -7084,7 +7036,7 @@
         <v>85</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>85</v>
+        <v>314</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>85</v>
@@ -7102,10 +7054,10 @@
         <v>119</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>85</v>
@@ -7138,7 +7090,7 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>85</v>
+        <v>315</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -7156,10 +7108,10 @@
         <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AS34" t="s" s="2">
         <v>85</v>
@@ -11421,7 +11373,7 @@
         <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>561</v>
+        <v>85</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>85</v>
@@ -11439,7 +11391,7 @@
         <v>138</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11450,14 +11402,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -11479,16 +11431,16 @@
         <v>172</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11516,11 +11468,11 @@
         <v>230</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>570</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11537,7 +11489,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11564,27 +11516,27 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AQ68" t="s" s="2">
+      <c r="AR68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS68" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS68" t="s" s="2">
-        <v>574</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11607,19 +11559,19 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11668,7 +11620,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11698,10 +11650,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11712,10 +11664,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11741,13 +11693,13 @@
         <v>172</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11776,11 +11728,11 @@
         <v>175</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>588</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11797,7 +11749,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11812,7 +11764,7 @@
         <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>85</v>
@@ -11824,27 +11776,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AQ70" t="s" s="2">
+      <c r="AR70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS70" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS70" t="s" s="2">
-        <v>593</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11870,16 +11822,16 @@
         <v>172</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11907,11 +11859,11 @@
         <v>175</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11928,7 +11880,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11943,7 +11895,7 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>85</v>
@@ -11958,10 +11910,10 @@
         <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11972,10 +11924,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11998,16 +11950,16 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -12057,7 +12009,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -12084,27 +12036,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AP72" t="s" s="2">
+      <c r="AQ72" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="AQ72" t="s" s="2">
+      <c r="AR72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS72" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS72" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12127,16 +12079,16 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -12186,7 +12138,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -12213,27 +12165,27 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="AP73" t="s" s="2">
+      <c r="AQ73" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="AQ73" t="s" s="2">
+      <c r="AR73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS73" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS73" t="s" s="2">
-        <v>621</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12256,19 +12208,19 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -12317,7 +12269,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12329,28 +12281,28 @@
         <v>85</v>
       </c>
       <c r="AJ74" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="AK74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP74" t="s" s="2">
+      <c r="AQ74" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
@@ -12361,10 +12313,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12488,10 +12440,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12617,14 +12569,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12646,10 +12598,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>199</v>
@@ -12704,7 +12656,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12748,10 +12700,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12774,13 +12726,13 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12831,7 +12783,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12840,7 +12792,7 @@
         <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>107</v>
@@ -12861,10 +12813,10 @@
         <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12875,10 +12827,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12901,13 +12853,13 @@
         <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12958,7 +12910,7 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12967,7 +12919,7 @@
         <v>95</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>107</v>
@@ -12988,10 +12940,10 @@
         <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
@@ -13002,10 +12954,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13031,16 +12983,16 @@
         <v>172</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -13068,11 +13020,11 @@
         <v>119</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>655</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>85</v>
       </c>
@@ -13089,7 +13041,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13116,13 +13068,13 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AP80" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="AP80" t="s" s="2">
-        <v>657</v>
-      </c>
       <c r="AQ80" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
@@ -13133,10 +13085,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13162,16 +13114,16 @@
         <v>172</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>85</v>
@@ -13196,14 +13148,14 @@
         <v>85</v>
       </c>
       <c r="X81" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="Y81" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="Y81" t="s" s="2">
+      <c r="Z81" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>665</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>85</v>
       </c>
@@ -13220,7 +13172,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -13247,13 +13199,13 @@
         <v>85</v>
       </c>
       <c r="AO81" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="AP81" t="s" s="2">
-        <v>657</v>
-      </c>
       <c r="AQ81" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
@@ -13264,10 +13216,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13290,17 +13242,17 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13349,7 +13301,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13382,7 +13334,7 @@
         <v>85</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
@@ -13393,10 +13345,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13422,10 +13374,10 @@
         <v>212</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13476,7 +13428,7 @@
         <v>85</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13506,10 +13458,10 @@
         <v>85</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>85</v>
@@ -13520,10 +13472,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13546,16 +13498,16 @@
         <v>96</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13605,7 +13557,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13635,10 +13587,10 @@
         <v>85</v>
       </c>
       <c r="AP84" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
@@ -13649,10 +13601,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13675,16 +13627,16 @@
         <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13734,7 +13686,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13764,10 +13716,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13778,10 +13730,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13804,19 +13756,19 @@
         <v>96</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>85</v>
@@ -13853,7 +13805,7 @@
         <v>85</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AC86" s="2"/>
       <c r="AD86" t="s" s="2">
@@ -13863,7 +13815,7 @@
         <v>144</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -13875,28 +13827,28 @@
         <v>85</v>
       </c>
       <c r="AJ86" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="AK86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP86" t="s" s="2">
+      <c r="AQ86" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="AQ86" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -13907,10 +13859,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14034,10 +13986,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14163,14 +14115,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -14192,10 +14144,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>199</v>
@@ -14250,7 +14202,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14294,10 +14246,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14323,16 +14275,16 @@
         <v>172</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14381,7 +14333,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>95</v>
@@ -14408,7 +14360,7 @@
         <v>85</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>398</v>
@@ -14425,10 +14377,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14454,13 +14406,13 @@
         <v>483</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>487</v>
@@ -14500,17 +14452,19 @@
         <v>85</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AC91" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD91" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14519,7 +14473,7 @@
         <v>95</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>107</v>
@@ -14537,7 +14491,7 @@
         <v>85</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>492</v>
@@ -14554,14 +14508,12 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>712</v>
+      </c>
+      <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>85</v>
       </c>
@@ -14579,22 +14531,22 @@
         <v>85</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>497</v>
+        <v>172</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>487</v>
+        <v>557</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14622,10 +14574,10 @@
         <v>230</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>488</v>
+        <v>558</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>489</v>
+        <v>559</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>85</v>
@@ -14643,7 +14595,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14652,13 +14604,13 @@
         <v>95</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>714</v>
+        <v>85</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>85</v>
@@ -14670,41 +14622,41 @@
         <v>85</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>712</v>
+        <v>85</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>492</v>
+        <v>138</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>493</v>
+        <v>561</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS92" t="s" s="2">
-        <v>494</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>85</v>
+        <v>563</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>85</v>
@@ -14716,16 +14668,16 @@
         <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>716</v>
+        <v>564</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>717</v>
+        <v>565</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>718</v>
+        <v>566</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14753,10 +14705,10 @@
         <v>230</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>85</v>
@@ -14774,22 +14726,22 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>719</v>
+        <v>85</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>720</v>
+        <v>85</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>85</v>
@@ -14801,31 +14753,31 @@
         <v>85</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>85</v>
+        <v>570</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>138</v>
+        <v>571</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS93" t="s" s="2">
-        <v>85</v>
+        <v>573</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>564</v>
+        <v>85</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -14844,19 +14796,19 @@
         <v>85</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>565</v>
+        <v>719</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>566</v>
+        <v>720</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>567</v>
+        <v>625</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>568</v>
+        <v>626</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -14881,13 +14833,13 @@
         <v>85</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>569</v>
+        <v>85</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>570</v>
+        <v>85</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>85</v>
@@ -14905,7 +14857,7 @@
         <v>85</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14932,29 +14884,31 @@
         <v>85</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>571</v>
+        <v>85</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>572</v>
+        <v>628</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>573</v>
+        <v>629</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS94" t="s" s="2">
-        <v>574</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C95" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="B95" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>85</v>
       </c>
@@ -14963,31 +14917,31 @@
         <v>83</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>86</v>
+        <v>622</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>723</v>
+        <v>689</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>724</v>
+        <v>690</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>626</v>
+        <v>691</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>627</v>
+        <v>692</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>85</v>
@@ -15036,7 +14990,7 @@
         <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>722</v>
+        <v>688</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -15048,7 +15002,7 @@
         <v>85</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>107</v>
+        <v>694</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>85</v>
@@ -15066,10 +15020,10 @@
         <v>85</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>629</v>
+        <v>695</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>630</v>
+        <v>696</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
@@ -15080,14 +15034,12 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>726</v>
-      </c>
+        <v>697</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>85</v>
       </c>
@@ -15099,29 +15051,25 @@
         <v>95</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>623</v>
+        <v>212</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>690</v>
+        <v>154</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>693</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>85</v>
       </c>
@@ -15169,19 +15117,19 @@
         <v>85</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>689</v>
+        <v>156</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>695</v>
+        <v>85</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>85</v>
@@ -15199,10 +15147,10 @@
         <v>85</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>696</v>
+        <v>85</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>697</v>
+        <v>158</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>85</v>
@@ -15213,21 +15161,21 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>698</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>85</v>
@@ -15239,15 +15187,17 @@
         <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>85</v>
@@ -15296,19 +15246,19 @@
         <v>85</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>85</v>
@@ -15340,14 +15290,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>699</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>196</v>
+        <v>633</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -15360,24 +15310,26 @@
         <v>85</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>214</v>
+        <v>634</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>215</v>
+        <v>635</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="O98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>85</v>
       </c>
@@ -15425,7 +15377,7 @@
         <v>85</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>162</v>
+        <v>636</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15458,7 +15410,7 @@
         <v>85</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>85</v>
@@ -15469,45 +15421,45 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>700</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>634</v>
+        <v>85</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>635</v>
+        <v>701</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>636</v>
+        <v>702</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>199</v>
+        <v>703</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>200</v>
+        <v>704</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>85</v>
@@ -15517,7 +15469,7 @@
         <v>85</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>85</v>
+        <v>727</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>85</v>
@@ -15532,13 +15484,13 @@
         <v>85</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>85</v>
@@ -15556,22 +15508,22 @@
         <v>85</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>637</v>
+        <v>700</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>85</v>
+        <v>728</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>85</v>
@@ -15583,16 +15535,16 @@
         <v>85</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>85</v>
+        <v>705</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>138</v>
+        <v>399</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>85</v>
@@ -15600,10 +15552,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15611,7 +15563,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>95</v>
@@ -15626,19 +15578,19 @@
         <v>96</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>172</v>
+        <v>483</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>705</v>
+        <v>487</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>85</v>
@@ -15648,7 +15600,7 @@
         <v>85</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>731</v>
+        <v>85</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>85</v>
@@ -15666,43 +15618,41 @@
         <v>230</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>394</v>
+        <v>488</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>395</v>
+        <v>489</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="AC100" s="2"/>
       <c r="AD100" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>85</v>
+        <v>710</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>732</v>
+        <v>85</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>85</v>
@@ -15714,29 +15664,31 @@
         <v>85</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>398</v>
+        <v>492</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>399</v>
+        <v>493</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AS100" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>706</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="D101" t="s" s="2">
         <v>85</v>
       </c>
@@ -15757,16 +15709,16 @@
         <v>96</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>483</v>
+        <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>487</v>
@@ -15794,29 +15746,31 @@
         <v>85</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>488</v>
+        <v>732</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>489</v>
+        <v>733</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AC101" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15825,25 +15779,25 @@
         <v>95</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>85</v>
+        <v>734</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>492</v>
@@ -15860,14 +15814,12 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>735</v>
-      </c>
+        <v>712</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>85</v>
       </c>
@@ -15885,22 +15837,22 @@
         <v>85</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>172</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>487</v>
+        <v>557</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>85</v>
@@ -15928,10 +15880,10 @@
         <v>230</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>488</v>
+        <v>558</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>489</v>
+        <v>559</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>85</v>
@@ -15949,7 +15901,7 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15958,7 +15910,7 @@
         <v>95</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>107</v>
@@ -15976,19 +15928,19 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>712</v>
+        <v>85</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>492</v>
+        <v>138</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>493</v>
+        <v>561</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS102" t="s" s="2">
-        <v>494</v>
+        <v>85</v>
       </c>
     </row>
     <row r="103" hidden="true">
@@ -15996,18 +15948,18 @@
         <v>736</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>737</v>
+        <v>717</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>85</v>
+        <v>563</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>85</v>
@@ -16019,16 +15971,20 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>154</v>
+        <v>564</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>85</v>
       </c>
@@ -16052,13 +16008,13 @@
         <v>85</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>85</v>
+        <v>568</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>85</v>
+        <v>569</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>85</v>
@@ -16076,19 +16032,19 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>156</v>
+        <v>717</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>85</v>
@@ -16103,31 +16059,31 @@
         <v>85</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>85</v>
+        <v>570</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>85</v>
+        <v>571</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>158</v>
+        <v>572</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS103" t="s" s="2">
-        <v>85</v>
+        <v>573</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -16146,18 +16102,20 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>214</v>
+        <v>719</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>215</v>
+        <v>720</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>85</v>
       </c>
@@ -16193,19 +16151,19 @@
         <v>85</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>162</v>
+        <v>718</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -16217,7 +16175,7 @@
         <v>85</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>85</v>
@@ -16235,10 +16193,10 @@
         <v>85</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>85</v>
+        <v>628</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>158</v>
+        <v>629</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>85</v>
@@ -16249,12 +16207,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="C105" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>739</v>
+      </c>
       <c r="D105" t="s" s="2">
         <v>85</v>
       </c>
@@ -16263,7 +16223,7 @@
         <v>83</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>96</v>
@@ -16275,19 +16235,19 @@
         <v>96</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>322</v>
+        <v>622</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>323</v>
+        <v>689</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>324</v>
+        <v>690</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>325</v>
+        <v>691</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>326</v>
+        <v>692</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>85</v>
@@ -16312,13 +16272,13 @@
         <v>85</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>742</v>
+        <v>85</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>743</v>
+        <v>85</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>85</v>
@@ -16336,7 +16296,7 @@
         <v>85</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>327</v>
+        <v>688</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>83</v>
@@ -16348,16 +16308,16 @@
         <v>85</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>107</v>
+        <v>694</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>744</v>
+        <v>85</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>85</v>
@@ -16366,10 +16326,10 @@
         <v>85</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>328</v>
+        <v>695</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>329</v>
+        <v>696</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>85</v>
@@ -16380,10 +16340,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>746</v>
+        <v>697</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16403,23 +16363,19 @@
         <v>85</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>212</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>381</v>
+        <v>154</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>85</v>
       </c>
@@ -16467,7 +16423,7 @@
         <v>85</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>385</v>
+        <v>156</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>83</v>
@@ -16479,7 +16435,7 @@
         <v>85</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>85</v>
@@ -16497,10 +16453,10 @@
         <v>85</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>386</v>
+        <v>85</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>387</v>
+        <v>158</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>85</v>
@@ -16511,24 +16467,24 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>715</v>
+        <v>698</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>85</v>
@@ -16537,20 +16493,18 @@
         <v>85</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>716</v>
+        <v>214</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>717</v>
+        <v>215</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>85</v>
       </c>
@@ -16574,13 +16528,13 @@
         <v>85</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>558</v>
+        <v>85</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>559</v>
+        <v>85</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>85</v>
@@ -16598,19 +16552,19 @@
         <v>85</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>715</v>
+        <v>162</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>719</v>
+        <v>85</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>85</v>
@@ -16628,10 +16582,10 @@
         <v>85</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>562</v>
+        <v>158</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>85</v>
@@ -16642,14 +16596,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>721</v>
+        <v>699</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>564</v>
+        <v>633</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -16662,25 +16616,25 @@
         <v>85</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>565</v>
+        <v>634</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>566</v>
+        <v>635</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>567</v>
+        <v>199</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>568</v>
+        <v>200</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>85</v>
@@ -16705,13 +16659,13 @@
         <v>85</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>569</v>
+        <v>85</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>570</v>
+        <v>85</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>85</v>
@@ -16729,7 +16683,7 @@
         <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>721</v>
+        <v>636</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>83</v>
@@ -16741,7 +16695,7 @@
         <v>85</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>85</v>
@@ -16756,27 +16710,27 @@
         <v>85</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>571</v>
+        <v>85</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>572</v>
+        <v>85</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>573</v>
+        <v>138</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS108" t="s" s="2">
-        <v>574</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>722</v>
+        <v>700</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16784,34 +16738,34 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>723</v>
+        <v>701</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>724</v>
+        <v>702</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>626</v>
+        <v>703</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>627</v>
+        <v>704</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>85</v>
@@ -16821,7 +16775,7 @@
         <v>85</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>85</v>
+        <v>727</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>85</v>
@@ -16836,13 +16790,13 @@
         <v>85</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>85</v>
@@ -16860,13 +16814,13 @@
         <v>85</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>722</v>
+        <v>700</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>85</v>
@@ -16875,7 +16829,7 @@
         <v>107</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>85</v>
+        <v>744</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>85</v>
@@ -16887,16 +16841,16 @@
         <v>85</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>85</v>
+        <v>705</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>629</v>
+        <v>398</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>630</v>
+        <v>399</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AS109" t="s" s="2">
         <v>85</v>
@@ -16904,14 +16858,12 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>751</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>85</v>
       </c>
@@ -16932,19 +16884,19 @@
         <v>96</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>623</v>
+        <v>483</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>693</v>
+        <v>487</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>85</v>
@@ -16969,43 +16921,41 @@
         <v>85</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>85</v>
+        <v>488</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>85</v>
+        <v>489</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>689</v>
+        <v>706</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>85</v>
+        <v>710</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>695</v>
+        <v>107</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>85</v>
@@ -17020,29 +16970,31 @@
         <v>85</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>85</v>
+        <v>711</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>696</v>
+        <v>492</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>697</v>
+        <v>493</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS110" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="C111" s="2"/>
+        <v>706</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="D111" t="s" s="2">
         <v>85</v>
       </c>
@@ -17054,25 +17006,29 @@
         <v>95</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>154</v>
+        <v>707</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>85</v>
       </c>
@@ -17096,13 +17052,13 @@
         <v>85</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>85</v>
+        <v>747</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>85</v>
+        <v>748</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>85</v>
@@ -17120,7 +17076,7 @@
         <v>85</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>156</v>
+        <v>706</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>83</v>
@@ -17129,59 +17085,59 @@
         <v>95</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>85</v>
+        <v>710</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>85</v>
+        <v>749</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>85</v>
+        <v>711</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>158</v>
+        <v>493</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS111" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>85</v>
@@ -17190,18 +17146,20 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>214</v>
+        <v>713</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>215</v>
+        <v>714</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O112" s="2"/>
+        <v>715</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>85</v>
       </c>
@@ -17225,13 +17183,13 @@
         <v>85</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>85</v>
+        <v>558</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>85</v>
+        <v>559</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>85</v>
@@ -17249,19 +17207,19 @@
         <v>85</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>162</v>
+        <v>712</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>85</v>
+        <v>716</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>85</v>
@@ -17279,10 +17237,10 @@
         <v>85</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>158</v>
+        <v>561</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>85</v>
@@ -17293,14 +17251,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>634</v>
+        <v>563</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -17313,25 +17271,25 @@
         <v>85</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>635</v>
+        <v>564</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>636</v>
+        <v>565</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>199</v>
+        <v>566</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>200</v>
+        <v>567</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>85</v>
@@ -17356,13 +17314,13 @@
         <v>85</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>85</v>
+        <v>568</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>85</v>
+        <v>569</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>85</v>
@@ -17380,7 +17338,7 @@
         <v>85</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>637</v>
+        <v>717</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
@@ -17392,7 +17350,7 @@
         <v>85</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>85</v>
@@ -17407,27 +17365,27 @@
         <v>85</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>85</v>
+        <v>570</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>85</v>
+        <v>571</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>138</v>
+        <v>572</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS113" t="s" s="2">
-        <v>85</v>
+        <v>573</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17435,34 +17393,34 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>702</v>
+        <v>719</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>704</v>
+        <v>625</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>705</v>
+        <v>626</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>85</v>
@@ -17472,7 +17430,7 @@
         <v>85</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>731</v>
+        <v>85</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>85</v>
@@ -17487,13 +17445,13 @@
         <v>85</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>394</v>
+        <v>85</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>395</v>
+        <v>85</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>85</v>
@@ -17511,13 +17469,13 @@
         <v>85</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>85</v>
@@ -17526,7 +17484,7 @@
         <v>107</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>756</v>
+        <v>85</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>85</v>
@@ -17538,1196 +17496,23 @@
         <v>85</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>706</v>
+        <v>85</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>398</v>
+        <v>628</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>399</v>
+        <v>629</v>
       </c>
       <c r="AR114" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AS114" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AC115" s="2"/>
-      <c r="AD115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AQ115" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AR115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS115" t="s" s="2">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="D116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="AP116" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AQ116" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AR116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS116" t="s" s="2">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ117" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AR117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS117" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ118" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AR118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS118" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AQ119" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AR119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS119" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AQ120" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AR120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS120" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="P121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AQ121" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AR121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS121" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AQ122" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AR122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS122" t="s" s="2">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AQ123" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AR123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS123" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS123">
+  <autoFilter ref="A1:AS114">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18737,7 +17522,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI122">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSigns.xlsx
+++ b/docs/StructureDefinition-VitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
